--- a/hanmi/dist/20261028_韓美半導體個股模型_v0.2.3.xlsx
+++ b/hanmi/dist/20261028_韓美半導體個股模型_v0.2.3.xlsx
@@ -5182,26 +5182,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5775,26 +5775,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6230,26 +6230,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9262,26 +9262,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9300,7 +9300,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D26:F26</t>
+      <t xml:space="preserve">In!D21:F21</t>
     </r>
   </si>
   <si>
@@ -9471,26 +9471,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9509,7 +9509,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D27:F27</t>
+      <t xml:space="preserve">In!D22:F22</t>
     </r>
   </si>
   <si>
@@ -9574,26 +9574,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9612,7 +9612,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D28:F28</t>
+      <t xml:space="preserve">In!D23:F23</t>
     </r>
   </si>
   <si>
@@ -9677,26 +9677,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9715,7 +9715,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D29:F29</t>
+      <t xml:space="preserve">In!D24:F24</t>
     </r>
   </si>
   <si>
@@ -9780,26 +9780,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9818,7 +9818,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">In!D47:F47</t>
+      <t xml:space="preserve">In!D42:F42</t>
     </r>
   </si>
   <si>

--- a/hanmi/dist/20261028_韓美半導體個股模型_v0.2.3.xlsx
+++ b/hanmi/dist/20261028_韓美半導體個股模型_v0.2.3.xlsx
@@ -4814,7 +4814,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -4833,7 +4833,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5407,7 +5407,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -5426,7 +5426,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5862,7 +5862,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -5881,7 +5881,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8894,7 +8894,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -8913,7 +8913,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9103,7 +9103,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -9122,7 +9122,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9206,7 +9206,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -9225,7 +9225,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9309,7 +9309,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -9328,7 +9328,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9412,7 +9412,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -9431,7 +9431,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9505,7 +9505,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261028_</t>
+      <t xml:space="preserve">samsung/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9524,7 +9524,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9598,7 +9598,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261028_</t>
+      <t xml:space="preserve">samsung/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9617,7 +9617,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9691,7 +9691,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261028_</t>
+      <t xml:space="preserve">samsung/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9710,7 +9710,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9784,7 +9784,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261028_</t>
+      <t xml:space="preserve">samsung/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9803,7 +9803,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9877,7 +9877,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">samsung/dist/20261028_</t>
+      <t xml:space="preserve">samsung/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9896,7 +9896,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9970,7 +9970,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261028_</t>
+      <t xml:space="preserve">micron/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9989,7 +9989,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10063,7 +10063,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261028_</t>
+      <t xml:space="preserve">micron/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -10082,7 +10082,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10156,7 +10156,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261028_</t>
+      <t xml:space="preserve">micron/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -10175,7 +10175,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10249,7 +10249,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261028_</t>
+      <t xml:space="preserve">micron/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -10268,7 +10268,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10342,7 +10342,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">micron/dist/20261028_</t>
+      <t xml:space="preserve">micron/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -10361,7 +10361,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.4.3.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/hanmi/dist/20261028_韓美半導體個股模型_v0.2.3.xlsx
+++ b/hanmi/dist/20261028_韓美半導體個股模型_v0.2.3.xlsx
@@ -9524,7 +9524,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.3.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9617,7 +9617,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.3.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9710,7 +9710,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.3.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9803,7 +9803,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.3.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9896,7 +9896,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.3.xlsx</t>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
